--- a/site/exports/bnu-sociology.xlsx
+++ b/site/exports/bnu-sociology.xlsx
@@ -452,8 +452,8 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">

--- a/site/exports/bnu-sociology.xlsx
+++ b/site/exports/bnu-sociology.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -675,12 +675,120 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张冠李</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>社会学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Partial purposeful official biography, not exhaustive career or bibliography.；Independent directory and current employment unknown; source present-tense labels are not current-personnel certification.；Degree labels/graduation alone leave degree_awarded unknown; study endpoints are not conferral dates.；Own advisors not stated in retained evidence; student-supervision titles and project leaders do not establish personal mentors.；Necessary professional excerpts only; no original HTTP/full-page archive or publisher metadata authentication.；Dual-bachelor label is one source education record, not two confirmed awarded qualifications.；Two masters study intervals overlap as reported; no reconciliation inferred.；Source year/volume metadata retained as listed, not independently corrected.；来源差异/限制：Page heading says 副教授 while biography says 讲师; no temporal reconciliation or current-rank certification.；来源差异/限制：Biography geography/environment; education field human geography; degree box Doctor of Science. Kept as different labels for one doctorate, not extra awards.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>谭江华</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>社会学院</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Partial purposeful official biography, not exhaustive career or bibliography.；Independent directory and current employment unknown; source present-tense labels are not current-personnel certification.；Degree labels/graduation alone leave degree_awarded unknown; study endpoints are not conferral dates.；Own advisors not stated in retained evidence; student-supervision titles and project leaders do not establish personal mentors.；Necessary professional excerpts only; no original HTTP/full-page archive or publisher metadata authentication.；Nankai graduation not explicitly tied to doctorate; degree institution remains unknown.；Only one named work retained; no inference of absence of other works. Historical department and college page are separate institutional labels.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -692,11 +800,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22.4" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -774,7 +882,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1897,8 +2005,606 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>张冠李</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>牛津大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>人文地理学</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>张冠李</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>伦敦政治经济学院</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>历史学</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>张冠李</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>法学硕士</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>国际政治</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源degree_as_source：法学硕士；来源level_as_source：硕士；来源层次标签：硕士</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>张冠李</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>法学与经济学双学士</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源degree_as_source：法学与经济学双学士；来源level_as_source：学士；来源层次标签：学士</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>张冠李</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>清华大学社会学系</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Work-experience listing; role unspecified and not classified as postdoctoral training.；任职按留存来源表述保留；不据此认证当前人事状态。；来源institution_as_source：清华大学社会学系</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>谭江华</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>法学博士</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源degree_as_source：法学博士；来源level_as_source：博士；来源层次标签：博士</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>谭江华</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>毕业</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>南开大学社会学系</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Graduation statement not explicitly tied to doctorate; not merged into degree institution.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（episode_type）：毕业；来源记载（毕业日期）：2007-07</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>谭江华</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>美国波士顿大学</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Nondegree episode classification, not denial of person qualifications. Dates and sequence unknown.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（episode_type）：访问学者</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>谭江华</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>哈佛大学</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Nondegree episode classification, not denial of person qualifications. Dates and sequence unknown.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（episode_type）：访问学者</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>谭江华</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>任教</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学社会学系</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2007-08</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>至今</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：任教；来源institution_as_source：北京师范大学社会学系</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S15"/>
+  <autoFilter ref="A1:S25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1919,6 +2625,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2021,7 +2737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2029,11 +2745,11 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="39.2" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="49" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="54.59999999999999" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -2270,8 +2986,166 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张冠李</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>提供、保护和参与：城市流动儿童数字使用鸿沟的田野调查</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_profile</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：张冰怡;张冠李；来源书目信息（期）：No.358 (05)；来源书目信息（页码）：40-48+112</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>张冠李</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Migrant children's digital divide in online learning during the Covid-19 pandemic: evidence from Stone School in Hangzhou, China</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_profile</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Zhang, Guanli; Zhou, Muzhi; Walker, Robert; Yang, Lichao；来源书目信息（卷）：57；来源书目信息（期）：1；来源书目信息（页码）：91-116</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>谭江华</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>中国法治现代化进路及其困厄</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>monograph_as_official_profile</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_contribution_role_as_source：个人主要成果中的专著列目；未独立核验作者题名；来源书目信息（出版日期）：2013-09</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -2279,6 +3153,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2290,14 +3170,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="46.2" customWidth="1" min="2" max="2"/>
+    <col width="64.39999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="60.2" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2564,27 +3444,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>付媛媛</t>
+          <t>张冠李</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>institution-classification-2</t>
+          <t>new-recovery-bnu-zhangguanli-s001-697f1e550eef</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>https://www.jlu.edu.cn/xxgk.htm</t>
+          <t>https://faculty.bnu.edu.cn/zhangguanli/zh_CN/index.htm</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>未单独记录</t>
+          <t>2026-10-25T06:18:36Z</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2601,42 +3481,116 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>谭江华</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-tanjianghua-s001-1b456ed2821b</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://soc.bnu.edu.cn/szdw/zzjs/fjs/8717c704158e45bfa78697e4d1f72d75.htm</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T06:18:36Z</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>付媛媛</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>institution-classification-2</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jlu.edu.cn/xxgk.htm</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>未单独记录</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>付媛媛</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>institution-classification-3</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>未单独记录</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>bnu</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2646,6 +3600,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/bnu-sociology.xlsx
+++ b/site/exports/bnu-sociology.xlsx
@@ -2184,7 +2184,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
